--- a/resourses/Laptops_Bulk_Import_Final.xlsx
+++ b/resourses/Laptops_Bulk_Import_Final.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>warranty</t>
+          <t>warrantyExpiry</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
